--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="D20" t="n">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="21">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D42" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="43">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D54" t="n">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="55">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3261</v>
+        <v>3262</v>
       </c>
       <c r="D85" t="n">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="86">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="D20" t="n">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="21">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D45" t="n">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="46">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3262</v>
+        <v>3263</v>
       </c>
       <c r="D85" t="n">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="86">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="D20" t="n">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="21">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D42" t="n">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="43">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D45" t="n">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="46">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="D54" t="n">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="55">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="D85" t="n">
-        <v>1697</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="86">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="D4" t="n">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="5">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="D16" t="n">
-        <v>1186</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="17">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="D20" t="n">
-        <v>1484</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="21">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D42" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="43">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="D45" t="n">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="46">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="D54" t="n">
-        <v>1353</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="55">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D62" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63">
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="D64" t="n">
-        <v>1368</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="65">
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D68" t="n">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="69">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3261</v>
+        <v>3266</v>
       </c>
       <c r="D85" t="n">
-        <v>1695</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="86">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="D4" t="n">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="5">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>107</v>
+      </c>
+      <c r="D15" t="n">
         <v>106</v>
-      </c>
-      <c r="D15" t="n">
-        <v>105</v>
       </c>
     </row>
     <row r="16">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="D20" t="n">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="21">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D42" t="n">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="43">
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D64" t="n">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="65">
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D68" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="69">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D69" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="D85" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="86">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="D4" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="5">
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D13" t="n">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="14">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D20" t="n">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="21">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D54" t="n">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="55">
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="D64" t="n">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="65">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="D85" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="86">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Birds/abundance.xlsx
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D40" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41">
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="C58" t="n">
+        <v>87</v>
+      </c>
+      <c r="D58" t="n">
         <v>86</v>
-      </c>
-      <c r="D58" t="n">
-        <v>85</v>
       </c>
     </row>
     <row r="59">
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D68" t="n">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="69">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D76" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D77" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78">
